--- a/test_samples/EXPRESS_MAXIMUM/sample2_ref.xlsx
+++ b/test_samples/EXPRESS_MAXIMUM/sample2_ref.xlsx
@@ -1,150 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\LC\供應商帳單\15. PT. Express Maximum___________測試OK\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19FF2B2-4FEE-4275-9F0A-A2C31BF92EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15465" yWindow="-13620" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15465" yWindow="-13620" windowWidth="24240" windowHeight="13020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EXPRESS_MAXIMUM" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXPRESS_MAXIMUM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
-  <si>
-    <t>INVOICE DATE
-發票日期</t>
-  </si>
-  <si>
-    <t>INVOICE NO
-發票號碼</t>
-  </si>
-  <si>
-    <t>SUPPLIER
-供應商名稱</t>
-  </si>
-  <si>
-    <t>CONSIGNEE
-集團公司名稱</t>
-  </si>
-  <si>
-    <t>Description
-費用名稱</t>
-  </si>
-  <si>
-    <t>AMOUNT
-金額</t>
-  </si>
-  <si>
-    <t>Order No.</t>
-  </si>
-  <si>
-    <t>Arrive Date
-到達日</t>
-  </si>
-  <si>
-    <t>on board date
-開船日</t>
-  </si>
-  <si>
-    <t>B/L NO.
-提單號碼</t>
-  </si>
-  <si>
-    <t>MBL NO.
-主提單號碼</t>
-  </si>
-  <si>
-    <t>Port of Loading
-啟運港</t>
-  </si>
-  <si>
-    <t>Port of discharge
-目的港</t>
-  </si>
-  <si>
-    <t>Volume
-材積</t>
-  </si>
-  <si>
-    <t>Vessel
-船名</t>
-  </si>
-  <si>
-    <t>Container no.
-貨櫃號碼</t>
-  </si>
-  <si>
-    <t>000001/HC-P/I/2026</t>
-  </si>
-  <si>
-    <t>PT. EXPRESS MAXIMUM</t>
-  </si>
-  <si>
-    <t>POUYUEN INDONESIA, PT</t>
-  </si>
-  <si>
-    <t>MESH</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>PLS12779396</t>
-  </si>
-  <si>
-    <t>FSC</t>
-  </si>
-  <si>
-    <t>N/A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -168,26 +65,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -475,165 +431,271 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="16" width="20" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
+    <row r="1" ht="29" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>INVOICE DATE
+發票日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>INVOICE NO
+發票號碼</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLIER
+供應商名稱</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CONSIGNEE
+集團公司名稱</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description
+費用名稱</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AMOUNT
+金額</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Order No.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Arrive Date
+到達日</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>on board date
+開船日</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>B/L NO.
+提單號碼</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MBL NO.
+主提單號碼</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Port of Loading
+啟運港</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Port of discharge
+目的港</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Volume
+材積</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Vessel
+船名</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Container no.
+貨櫃號碼</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2">
+      <c r="A2" s="2" t="n">
         <v>46024</v>
       </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000001/HC-P/I/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PT.EXPRESS MAXIMUM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>POUYUEN INDONESIA, PT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MESH</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>2264895</v>
       </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" t="s">
-        <v>20</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PLS12779396</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3">
+      <c r="A3" s="2" t="n">
         <v>46024</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000001/HC-P/I/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PT.EXPRESS MAXIMUM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>POUYUEN INDONESIA, PT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FSC</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>85059</v>
       </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" t="s">
-        <v>20</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>PLS12779396</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>